--- a/data/mt_gt/2_master_data/khách hàng.xlsx
+++ b/data/mt_gt/2_master_data/khách hàng.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/45e087e4394d60b0/Máy tính/1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\OneDrive\Máy tính\1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{921AF126-26F1-4DEB-A852-5E6043CD089B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAA9EC7C-D563-4B96-959A-F147A269EC27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{96465113-FD64-440C-BE95-D04BABE0A104}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{F35554EB-9677-436C-B69D-79E35A1087D5}"/>
   </bookViews>
   <sheets>
     <sheet name="3DS khách hàng mới-Vũ" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'3DS khách hàng mới-Vũ'!$A$1:$B$69</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="168">
   <si>
     <t>Mã khách hàng</t>
   </si>
@@ -264,7 +267,7 @@
     <t>0313612829</t>
   </si>
   <si>
-    <t>CÔNG TY CỔ PHẦN HASAKI VIETNAM</t>
+    <t>Hasaki</t>
   </si>
   <si>
     <t>001184021443</t>
@@ -336,7 +339,199 @@
     <t>Benstore</t>
   </si>
   <si>
-    <t>Shop Benstore</t>
+    <t>BEN STORE</t>
+  </si>
+  <si>
+    <t>0105353644</t>
+  </si>
+  <si>
+    <t>MORAGAN MART</t>
+  </si>
+  <si>
+    <t>2902249239</t>
+  </si>
+  <si>
+    <t>AYRA VN</t>
+  </si>
+  <si>
+    <t>001192028402</t>
+  </si>
+  <si>
+    <t>HKD NGÔ THỊ DIỆU LINH</t>
+  </si>
+  <si>
+    <t>064185002731</t>
+  </si>
+  <si>
+    <t>Trần Mỹ Hạnh-TOÀN CẦU</t>
+  </si>
+  <si>
+    <t>0310618188-009</t>
+  </si>
+  <si>
+    <t>084187011649</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SHOPTRANSHOP</t>
+  </si>
+  <si>
+    <t>0909022503</t>
+  </si>
+  <si>
+    <t>NHÀ THUỐC MAI HƯƠNG</t>
+  </si>
+  <si>
+    <t>082198000264</t>
+  </si>
+  <si>
+    <t>Trương Hồng Ngọc Châu</t>
+  </si>
+  <si>
+    <t>0105696842</t>
+  </si>
+  <si>
+    <t>Top Market -EB</t>
+  </si>
+  <si>
+    <t>3604065809</t>
+  </si>
+  <si>
+    <t>3901377078</t>
+  </si>
+  <si>
+    <t>BANGKOK MART</t>
+  </si>
+  <si>
+    <t>0402044529</t>
+  </si>
+  <si>
+    <t>HOMIMART</t>
+  </si>
+  <si>
+    <t>0110681545</t>
+  </si>
+  <si>
+    <t>BẢO NGÂN - Wefresh</t>
+  </si>
+  <si>
+    <t>1001073066</t>
+  </si>
+  <si>
+    <t>CÔNG TY TNHH DƯỢC VẬT TƯ Y TẾ 242</t>
+  </si>
+  <si>
+    <t>0107499688</t>
+  </si>
+  <si>
+    <t>TOMITA</t>
+  </si>
+  <si>
+    <t>0969897207</t>
+  </si>
+  <si>
+    <t>MOON STORE</t>
+  </si>
+  <si>
+    <t>1702329333</t>
+  </si>
+  <si>
+    <t>KINGKONG PQ</t>
+  </si>
+  <si>
+    <t>0111423723</t>
+  </si>
+  <si>
+    <t>HD COSME</t>
+  </si>
+  <si>
+    <t>048184001346</t>
+  </si>
+  <si>
+    <t>THANH HÀ FRUIT</t>
+  </si>
+  <si>
+    <t>033093003510</t>
+  </si>
+  <si>
+    <t>HKD NGUYỄN QUANG THẮNG</t>
+  </si>
+  <si>
+    <t>0317336175</t>
+  </si>
+  <si>
+    <t>ABETTERLIFE (AGOURMET)</t>
+  </si>
+  <si>
+    <t>4200559628</t>
+  </si>
+  <si>
+    <t>HÓA MỸ PHẨM TỰ NHIÊN</t>
+  </si>
+  <si>
+    <t>031173002959</t>
+  </si>
+  <si>
+    <t>NATURALLY VIỆT NAM</t>
+  </si>
+  <si>
+    <t>0110981475</t>
+  </si>
+  <si>
+    <t>KINDERGARDEN</t>
+  </si>
+  <si>
+    <t>0402281209</t>
+  </si>
+  <si>
+    <t>CÔNG TY TNHH ABC PHARMACARE</t>
+  </si>
+  <si>
+    <t>4201557327</t>
+  </si>
+  <si>
+    <t>CÔNG TY CỔ PHẦN AMART</t>
+  </si>
+  <si>
+    <t>0985786630</t>
+  </si>
+  <si>
+    <t>Mộc Beautiful</t>
+  </si>
+  <si>
+    <t>0987520530</t>
+  </si>
+  <si>
+    <t>Chị Hương</t>
+  </si>
+  <si>
+    <t>037186007422</t>
+  </si>
+  <si>
+    <t>Phạm Thị Linh  (LINH EU)</t>
+  </si>
+  <si>
+    <t>0110809611</t>
+  </si>
+  <si>
+    <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ THIẾT BỊ TÂM ANH</t>
+  </si>
+  <si>
+    <t>0315127257</t>
+  </si>
+  <si>
+    <t>PICARE VIET NAM</t>
+  </si>
+  <si>
+    <t>0963399320</t>
+  </si>
+  <si>
+    <t>Thảo Moon -0963399320</t>
+  </si>
+  <si>
+    <t>001094006749</t>
+  </si>
+  <si>
+    <t>HỘ KINH DOANH NGUYỄN QUANG HUY 1994</t>
   </si>
 </sst>
 </file>
@@ -722,11 +917,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFAF9749-8D82-4CEA-9B29-ED93B06567C6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89A10076-77B5-48B2-B0EA-152A1255F653}">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B86"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="1"/>
@@ -1157,7 +1352,272 @@
         <v>103</v>
       </c>
     </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>104</v>
+      </c>
+      <c r="B54" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>110</v>
+      </c>
+      <c r="B57" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>113</v>
+      </c>
+      <c r="B59" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>115</v>
+      </c>
+      <c r="B60" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>117</v>
+      </c>
+      <c r="B61" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>124</v>
+      </c>
+      <c r="B65" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>126</v>
+      </c>
+      <c r="B66" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>130</v>
+      </c>
+      <c r="B68" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>140</v>
+      </c>
+      <c r="B73" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>148</v>
+      </c>
+      <c r="B77" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>150</v>
+      </c>
+      <c r="B78" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>152</v>
+      </c>
+      <c r="B79" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>154</v>
+      </c>
+      <c r="B80" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:B69" xr:uid="{59CBFC0D-FCE7-40E8-8681-D5FAD98A8AC3}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>